--- a/Production/Pyopticl parts list.xlsx
+++ b/Production/Pyopticl parts list.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kim/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kim/Desktop/Lab/Github/PyOpticL_Rubidium_System/Production/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D108276-B69B-6E44-AA05-024C109EBE88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCF47C21-431D-DA41-97CC-6E1B30686599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9800" yWindow="740" windowWidth="19600" windowHeight="16680" xr2:uid="{2C0518BD-81B3-2E40-93F6-7012D65C5310}"/>
+    <workbookView xWindow="14700" yWindow="740" windowWidth="14700" windowHeight="16680" xr2:uid="{2C0518BD-81B3-2E40-93F6-7012D65C5310}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="57">
   <si>
     <t>Adaptors</t>
   </si>
@@ -170,9 +170,6 @@
     <t>3*Laser Board2</t>
   </si>
   <si>
-    <t>2*TA_Baseplate_V2</t>
-  </si>
-  <si>
     <t>3*Repumper_Baseplate_consolidated</t>
   </si>
   <si>
@@ -195,6 +192,21 @@
   </si>
   <si>
     <t>Repumper_Baseplate_consolidated.step</t>
+  </si>
+  <si>
+    <t>3*TA_Baseplate_V2</t>
+  </si>
+  <si>
+    <t>2*SAS Board</t>
+  </si>
+  <si>
+    <t>6*TA_Baseplate_V2</t>
+  </si>
+  <si>
+    <t>0*Repumper_Baseplate_consolidated</t>
+  </si>
+  <si>
+    <t>0*AOM Board</t>
   </si>
 </sst>
 </file>
@@ -262,26 +274,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -429,12 +421,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -448,94 +462,88 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -887,17 +895,17 @@
         <v>43</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K3" s="2"/>
     </row>
@@ -1101,7 +1109,7 @@
     </row>
     <row r="11" spans="2:11" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C11" s="1">
         <v>1</v>
@@ -1119,7 +1127,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I11" s="2">
         <v>1</v>
@@ -1133,10 +1141,10 @@
     </row>
     <row r="12" spans="2:11" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -1376,16 +1384,16 @@
       </c>
     </row>
     <row r="24" spans="2:11" s="4" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="33" t="s">
+      <c r="B24" s="28" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="4">
         <v>1</v>
       </c>
-      <c r="J24" s="33" t="s">
+      <c r="J24" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="K24" s="34">
+      <c r="K24" s="29">
         <v>1</v>
       </c>
     </row>
@@ -1422,13 +1430,13 @@
       </c>
     </row>
     <row r="26" spans="2:11" s="4" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D26" s="33" t="s">
+      <c r="D26" s="28" t="s">
         <v>23</v>
       </c>
       <c r="E26" s="4">
         <v>2</v>
       </c>
-      <c r="F26" s="33" t="s">
+      <c r="F26" s="28" t="s">
         <v>23</v>
       </c>
       <c r="G26" s="4">
@@ -1444,22 +1452,22 @@
       </c>
     </row>
     <row r="28" spans="2:11" s="4" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D28" s="33" t="s">
+      <c r="D28" s="28" t="s">
         <v>24</v>
       </c>
       <c r="E28" s="4">
         <v>1</v>
       </c>
-      <c r="F28" s="33" t="s">
+      <c r="F28" s="28" t="s">
         <v>24</v>
       </c>
       <c r="G28" s="4">
         <v>1</v>
       </c>
-      <c r="J28" s="33" t="s">
+      <c r="J28" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="K28" s="34">
+      <c r="K28" s="29">
         <v>1</v>
       </c>
     </row>
@@ -1484,22 +1492,22 @@
       </c>
     </row>
     <row r="30" spans="2:11" s="4" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D30" s="33" t="s">
+      <c r="D30" s="28" t="s">
         <v>26</v>
       </c>
       <c r="E30" s="4">
         <v>1</v>
       </c>
-      <c r="F30" s="33" t="s">
+      <c r="F30" s="28" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="4">
         <v>1</v>
       </c>
-      <c r="J30" s="33" t="s">
+      <c r="J30" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="K30" s="34">
+      <c r="K30" s="29">
         <v>1</v>
       </c>
     </row>
@@ -1512,10 +1520,10 @@
       </c>
     </row>
     <row r="32" spans="2:11" s="4" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H32" s="33" t="s">
+      <c r="H32" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I32" s="34">
+      <c r="I32" s="29">
         <v>1</v>
       </c>
     </row>
@@ -1554,457 +1562,457 @@
     <row r="34" spans="2:11" s="4" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="35" spans="2:11" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="2:11" s="4" customFormat="1" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="14"/>
-      <c r="C36" s="17" t="s">
+      <c r="B36" s="9"/>
+      <c r="C36" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D36" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="E36" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="F36" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="G36" s="13" t="s">
+      <c r="D36" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="F36" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H36" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="H36" s="14" t="s">
-        <v>48</v>
-      </c>
     </row>
     <row r="37" spans="2:11" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="10" t="s">
+      <c r="B37" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C37" s="18">
+      <c r="C37" s="13">
         <v>7</v>
       </c>
-      <c r="D37" s="26">
+      <c r="D37" s="21">
         <v>7</v>
       </c>
-      <c r="E37" s="26">
+      <c r="E37" s="21">
         <v>7</v>
       </c>
-      <c r="F37" s="30">
+      <c r="F37" s="25">
         <v>4</v>
       </c>
-      <c r="G37" s="5">
+      <c r="G37" s="2">
         <v>4</v>
       </c>
-      <c r="H37" s="15">
-        <f>3*C37+2*D37+3*E37+F37+G37</f>
-        <v>64</v>
+      <c r="H37" s="30">
+        <f>3*C37+6*D37+2*F37</f>
+        <v>71</v>
       </c>
       <c r="I37" s="2"/>
     </row>
     <row r="38" spans="2:11" s="4" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="11" t="s">
+      <c r="B38" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C38" s="19">
-        <v>1</v>
-      </c>
-      <c r="D38" s="27">
-        <v>0</v>
-      </c>
-      <c r="E38" s="27">
-        <v>0</v>
-      </c>
-      <c r="F38" s="24">
-        <v>0</v>
-      </c>
-      <c r="G38" s="6">
-        <v>0</v>
-      </c>
-      <c r="H38" s="16">
-        <f>3*C38+2*D38+3*E38+F38+G38</f>
+      <c r="C38" s="14">
+        <v>1</v>
+      </c>
+      <c r="D38" s="22">
+        <v>0</v>
+      </c>
+      <c r="E38" s="22">
+        <v>0</v>
+      </c>
+      <c r="F38" s="19">
+        <v>0</v>
+      </c>
+      <c r="G38" s="4">
+        <v>0</v>
+      </c>
+      <c r="H38" s="11">
+        <f>3*C38+6*D38+2*F38</f>
         <v>3</v>
       </c>
     </row>
     <row r="39" spans="2:11" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="10" t="s">
+      <c r="B39" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C39" s="18">
-        <v>0</v>
-      </c>
-      <c r="D39" s="26">
-        <v>1</v>
-      </c>
-      <c r="E39" s="26">
-        <v>1</v>
-      </c>
-      <c r="F39" s="23">
-        <v>0</v>
-      </c>
-      <c r="G39" s="7">
-        <v>0</v>
-      </c>
-      <c r="H39" s="15">
-        <f t="shared" ref="H39:H54" si="0">3*C39+2*D39+3*E39+F39+G39</f>
+      <c r="C39" s="13">
+        <v>0</v>
+      </c>
+      <c r="D39" s="21">
+        <v>1</v>
+      </c>
+      <c r="E39" s="21">
+        <v>1</v>
+      </c>
+      <c r="F39" s="18">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0</v>
+      </c>
+      <c r="H39" s="10">
+        <f t="shared" ref="H39:H54" si="0">3*C39+6*D39+2*F39</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" s="4" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B40" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" s="14">
+        <v>2</v>
+      </c>
+      <c r="D40" s="22">
+        <v>2</v>
+      </c>
+      <c r="E40" s="22">
+        <v>2</v>
+      </c>
+      <c r="F40" s="26">
+        <v>1</v>
+      </c>
+      <c r="G40" s="29">
+        <v>1</v>
+      </c>
+      <c r="H40" s="11">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B41" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" s="13">
+        <v>2</v>
+      </c>
+      <c r="D41" s="21">
+        <v>2</v>
+      </c>
+      <c r="E41" s="21">
+        <v>2</v>
+      </c>
+      <c r="F41" s="25">
+        <v>1</v>
+      </c>
+      <c r="G41" s="2">
+        <v>1</v>
+      </c>
+      <c r="H41" s="10">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" s="4" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" s="14">
+        <v>2</v>
+      </c>
+      <c r="D42" s="22">
+        <v>2</v>
+      </c>
+      <c r="E42" s="22">
+        <v>2</v>
+      </c>
+      <c r="F42" s="26">
+        <v>1</v>
+      </c>
+      <c r="G42" s="29">
+        <v>1</v>
+      </c>
+      <c r="H42" s="11">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B43" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43" s="13">
+        <v>2</v>
+      </c>
+      <c r="D43" s="21">
+        <v>2</v>
+      </c>
+      <c r="E43" s="21">
+        <v>2</v>
+      </c>
+      <c r="F43" s="25">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2">
+        <v>1</v>
+      </c>
+      <c r="H43" s="10">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" s="4" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B44" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" s="14">
+        <v>2</v>
+      </c>
+      <c r="D44" s="22">
+        <v>3</v>
+      </c>
+      <c r="E44" s="22">
+        <v>3</v>
+      </c>
+      <c r="F44" s="26">
+        <v>4</v>
+      </c>
+      <c r="G44" s="29">
         <v>5</v>
       </c>
-    </row>
-    <row r="40" spans="2:11" s="4" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C40" s="19">
-        <v>2</v>
-      </c>
-      <c r="D40" s="27">
-        <v>2</v>
-      </c>
-      <c r="E40" s="27">
-        <v>2</v>
-      </c>
-      <c r="F40" s="31">
-        <v>1</v>
-      </c>
-      <c r="G40" s="8">
-        <v>1</v>
-      </c>
-      <c r="H40" s="16">
+      <c r="H44" s="11">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="41" spans="2:11" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B45" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="13">
+        <v>1</v>
+      </c>
+      <c r="D45" s="21">
+        <v>0</v>
+      </c>
+      <c r="E45" s="21">
+        <v>0</v>
+      </c>
+      <c r="F45" s="18">
+        <v>0</v>
+      </c>
+      <c r="G45" s="2">
+        <v>1</v>
+      </c>
+      <c r="H45" s="10">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" s="4" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B46" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C46" s="14">
+        <v>2</v>
+      </c>
+      <c r="D46" s="22">
+        <v>3</v>
+      </c>
+      <c r="E46" s="22">
+        <v>3</v>
+      </c>
+      <c r="F46" s="26">
+        <v>4</v>
+      </c>
+      <c r="G46" s="29">
+        <v>5</v>
+      </c>
+      <c r="H46" s="11">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B47" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C47" s="13">
+        <v>0</v>
+      </c>
+      <c r="D47" s="21">
+        <v>2</v>
+      </c>
+      <c r="E47" s="21">
+        <v>2</v>
+      </c>
+      <c r="F47" s="18">
+        <v>0</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0</v>
+      </c>
+      <c r="H47" s="10">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C41" s="18">
-        <v>2</v>
-      </c>
-      <c r="D41" s="26">
-        <v>2</v>
-      </c>
-      <c r="E41" s="26">
-        <v>2</v>
-      </c>
-      <c r="F41" s="30">
-        <v>1</v>
-      </c>
-      <c r="G41" s="5">
-        <v>1</v>
-      </c>
-      <c r="H41" s="15">
+    </row>
+    <row r="48" spans="2:11" s="4" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B48" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C48" s="14">
+        <v>0</v>
+      </c>
+      <c r="D48" s="22">
+        <v>0</v>
+      </c>
+      <c r="E48" s="22">
+        <v>0</v>
+      </c>
+      <c r="F48" s="19">
+        <v>0</v>
+      </c>
+      <c r="G48" s="29">
+        <v>2</v>
+      </c>
+      <c r="H48" s="11">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11" s="4" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" s="19">
-        <v>2</v>
-      </c>
-      <c r="D42" s="27">
-        <v>2</v>
-      </c>
-      <c r="E42" s="27">
-        <v>2</v>
-      </c>
-      <c r="F42" s="31">
-        <v>1</v>
-      </c>
-      <c r="G42" s="8">
-        <v>1</v>
-      </c>
-      <c r="H42" s="16">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="43" spans="2:11" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C43" s="18">
-        <v>2</v>
-      </c>
-      <c r="D43" s="26">
-        <v>2</v>
-      </c>
-      <c r="E43" s="26">
-        <v>2</v>
-      </c>
-      <c r="F43" s="30">
-        <v>1</v>
-      </c>
-      <c r="G43" s="5">
-        <v>1</v>
-      </c>
-      <c r="H43" s="15">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="2:11" s="4" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C44" s="19">
-        <v>2</v>
-      </c>
-      <c r="D44" s="27">
-        <v>3</v>
-      </c>
-      <c r="E44" s="27">
-        <v>3</v>
-      </c>
-      <c r="F44" s="31">
-        <v>4</v>
-      </c>
-      <c r="G44" s="8">
-        <v>5</v>
-      </c>
-      <c r="H44" s="16">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="45" spans="2:11" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="18">
-        <v>1</v>
-      </c>
-      <c r="D45" s="26">
-        <v>0</v>
-      </c>
-      <c r="E45" s="26">
-        <v>0</v>
-      </c>
-      <c r="F45" s="23">
-        <v>0</v>
-      </c>
-      <c r="G45" s="5">
-        <v>1</v>
-      </c>
-      <c r="H45" s="15">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="2:11" s="4" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C46" s="19">
-        <v>2</v>
-      </c>
-      <c r="D46" s="27">
-        <v>3</v>
-      </c>
-      <c r="E46" s="27">
-        <v>3</v>
-      </c>
-      <c r="F46" s="31">
-        <v>4</v>
-      </c>
-      <c r="G46" s="8">
-        <v>5</v>
-      </c>
-      <c r="H46" s="16">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="47" spans="2:11" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C47" s="18">
-        <v>0</v>
-      </c>
-      <c r="D47" s="26">
-        <v>2</v>
-      </c>
-      <c r="E47" s="26">
-        <v>2</v>
-      </c>
-      <c r="F47" s="23">
-        <v>0</v>
-      </c>
-      <c r="G47" s="7">
-        <v>0</v>
-      </c>
-      <c r="H47" s="15">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11" s="4" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="C48" s="19">
-        <v>0</v>
-      </c>
-      <c r="D48" s="27">
-        <v>0</v>
-      </c>
-      <c r="E48" s="27">
-        <v>0</v>
-      </c>
-      <c r="F48" s="24">
-        <v>0</v>
-      </c>
-      <c r="G48" s="8">
-        <v>2</v>
-      </c>
-      <c r="H48" s="16">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="10" t="s">
+      <c r="B49" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C49" s="18">
-        <v>0</v>
-      </c>
-      <c r="D49" s="26">
-        <v>1</v>
-      </c>
-      <c r="E49" s="26">
-        <v>1</v>
-      </c>
-      <c r="F49" s="23">
-        <v>0</v>
-      </c>
-      <c r="G49" s="5">
-        <v>1</v>
-      </c>
-      <c r="H49" s="15">
+      <c r="C49" s="13">
+        <v>0</v>
+      </c>
+      <c r="D49" s="21">
+        <v>1</v>
+      </c>
+      <c r="E49" s="21">
+        <v>1</v>
+      </c>
+      <c r="F49" s="18">
+        <v>0</v>
+      </c>
+      <c r="G49" s="2">
+        <v>1</v>
+      </c>
+      <c r="H49" s="10">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
     <row r="50" spans="2:8" s="4" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="11" t="s">
+      <c r="B50" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C50" s="19">
-        <v>0</v>
-      </c>
-      <c r="D50" s="27">
-        <v>1</v>
-      </c>
-      <c r="E50" s="27">
-        <v>1</v>
-      </c>
-      <c r="F50" s="24">
-        <v>0</v>
-      </c>
-      <c r="G50" s="8">
-        <v>1</v>
-      </c>
-      <c r="H50" s="16">
+      <c r="C50" s="14">
+        <v>0</v>
+      </c>
+      <c r="D50" s="22">
+        <v>1</v>
+      </c>
+      <c r="E50" s="22">
+        <v>1</v>
+      </c>
+      <c r="F50" s="19">
+        <v>0</v>
+      </c>
+      <c r="G50" s="29">
+        <v>1</v>
+      </c>
+      <c r="H50" s="11">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
     <row r="51" spans="2:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="10" t="s">
+      <c r="B51" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C51" s="18">
-        <v>0</v>
-      </c>
-      <c r="D51" s="26">
-        <v>1</v>
-      </c>
-      <c r="E51" s="26">
-        <v>1</v>
-      </c>
-      <c r="F51" s="23">
-        <v>0</v>
-      </c>
-      <c r="G51" s="5">
-        <v>1</v>
-      </c>
-      <c r="H51" s="15">
+      <c r="C51" s="13">
+        <v>0</v>
+      </c>
+      <c r="D51" s="21">
+        <v>1</v>
+      </c>
+      <c r="E51" s="21">
+        <v>1</v>
+      </c>
+      <c r="F51" s="18">
+        <v>0</v>
+      </c>
+      <c r="G51" s="2">
+        <v>1</v>
+      </c>
+      <c r="H51" s="10">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
     <row r="52" spans="2:8" s="4" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="11" t="s">
+      <c r="B52" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C52" s="20">
-        <v>0</v>
-      </c>
-      <c r="D52" s="27">
-        <v>0</v>
-      </c>
-      <c r="E52" s="27">
-        <v>0</v>
-      </c>
-      <c r="F52" s="31">
-        <v>1</v>
-      </c>
-      <c r="G52" s="6">
-        <v>0</v>
-      </c>
-      <c r="H52" s="16">
+      <c r="C52" s="15">
+        <v>0</v>
+      </c>
+      <c r="D52" s="22">
+        <v>0</v>
+      </c>
+      <c r="E52" s="22">
+        <v>0</v>
+      </c>
+      <c r="F52" s="26">
+        <v>1</v>
+      </c>
+      <c r="G52" s="4">
+        <v>0</v>
+      </c>
+      <c r="H52" s="11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="10" t="s">
+      <c r="B53" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C53" s="21">
-        <v>0</v>
-      </c>
-      <c r="D53" s="26">
-        <v>0</v>
-      </c>
-      <c r="E53" s="26">
-        <v>0</v>
-      </c>
-      <c r="F53" s="30">
-        <v>1</v>
-      </c>
-      <c r="G53" s="7">
-        <v>0</v>
-      </c>
-      <c r="H53" s="15">
+      <c r="C53" s="16">
+        <v>0</v>
+      </c>
+      <c r="D53" s="21">
+        <v>0</v>
+      </c>
+      <c r="E53" s="21">
+        <v>0</v>
+      </c>
+      <c r="F53" s="25">
+        <v>1</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0</v>
+      </c>
+      <c r="H53" s="10">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="2:8" s="4" customFormat="1" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="12" t="s">
+      <c r="B54" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C54" s="22">
-        <v>1</v>
-      </c>
-      <c r="D54" s="28">
-        <v>1</v>
-      </c>
-      <c r="E54" s="28">
-        <v>1</v>
-      </c>
-      <c r="F54" s="32">
+      <c r="C54" s="17">
+        <v>1</v>
+      </c>
+      <c r="D54" s="23">
+        <v>1</v>
+      </c>
+      <c r="E54" s="23">
+        <v>1</v>
+      </c>
+      <c r="F54" s="27">
         <v>3</v>
       </c>
-      <c r="G54" s="9">
-        <v>1</v>
-      </c>
-      <c r="H54" s="12">
+      <c r="G54" s="31">
+        <v>1</v>
+      </c>
+      <c r="H54" s="7">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/Production/Pyopticl parts list.xlsx
+++ b/Production/Pyopticl parts list.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kim/Desktop/Lab/Github/PyOpticL_Rubidium_System/Production/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCF47C21-431D-DA41-97CC-6E1B30686599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2904F97F-50AD-A44E-B569-9DC9913C8B43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14700" yWindow="740" windowWidth="14700" windowHeight="16680" xr2:uid="{2C0518BD-81B3-2E40-93F6-7012D65C5310}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16680" xr2:uid="{2C0518BD-81B3-2E40-93F6-7012D65C5310}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
